--- a/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
@@ -616,7 +616,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.12)</t>
+          <t>End-2026 target status assessment and reporting (v0.13)</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (click the ref to see your full SR25 response)</t>
+          <t>SR25 response</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -1065,9 +1065,8 @@
     <row r="20"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="H13:K13"/>
     <mergeCell ref="B4:C8"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="L13:R13"/>

--- a/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,18 +62,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <i val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <sz val="22"/>
@@ -117,8 +105,12 @@
       <name val="Aptos Narrow"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -128,11 +120,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000B3040"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -183,60 +170,54 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -620,13 +601,12 @@
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -637,450 +617,366 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.13)</t>
+          <t>SR26 sustainability reporting (v0.14)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>End-2026 target status confirmation and reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Target status assessment and definitions</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="B4" s="5" t="inlineStr">
+          <t>SR26 sustainability reporting request</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>• Confirm target status for each row below (Column L). Refer to target status definitions to the right for guidance.
-• Provide commentary on progress towards each target (Column M or N)
-• Provide supporting documentation if required (Column O), including links to images
-• Note the source of your information and any limitations (Column P), then confirm the information is accurate (Columns Q–R)
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
+• Provide supporting information if required (Column N), including links to documents or images
+• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
-• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch.
+• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
 • Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided demonstrates that the Faculty/Portfolio has met or exceeded the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided indicates that the target has not been met, but there has been a significant improvement and performance is trending towards the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>Some action has been taken to address the target, but the data and information provided demonstrates that this has been insufficient to meet the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>No action has been taken.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="L8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>Note: target status definitions are under review for 2027 reporting. 2026 ratings are for internal management reporting only.</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8" ht="60" customHeight="1"/>
     <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>CIOG – Responsible AI &amp; digital</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>Confirm end-2026 target status</t>
-        </is>
-      </c>
-      <c r="M14" s="15" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="N14" s="15" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="O14" s="15" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr">
+      <c r="O14" s="10" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="Q14" s="15" t="inlineStr">
+      <c r="P14" s="10" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="R14" s="15" t="inlineStr">
+      <c r="Q14" s="10" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr"/>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>(Met or exceeded; partially met; not met; not yet started)</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-A general update on activities in relation to the overarching target (Column D)</t>
-        </is>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-Data and commentary in direct response to the reporting request (Column F)</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>Provide any additional information to support the target status assessment (e.g. links, images, rationale for selection of target status)</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="inlineStr"/>
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>A general update on activities in relation to the overarching target (Column D)</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Data and commentary in direct response to the reporting request (Column F)</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Any additional information (e.g. links, images, documents)</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="Q15" s="16" t="inlineStr">
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="R15" s="16" t="inlineStr">
+      <c r="Q15" s="11" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>AI1(a)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Responsible AI</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Improve understanding of our sustainability-related risks and opportunities of AI technologies by 2028.</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Established measurement of estimated operational impacts and opportunities (eg operational impacts could include energy, water, emissions and intensity measures)</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>(Reporting request TBC)</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>We will provide a high-level overview of AI's estimated operational impacts and opportunities in 2026, ahead of more detailed measurement from 2027.</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr"/>
-      <c r="I16" s="19" t="inlineStr"/>
-      <c r="J16" s="19" t="inlineStr"/>
-      <c r="K16" s="19" t="inlineStr"/>
-      <c r="L16" s="20" t="n"/>
-      <c r="M16" s="20" t="n"/>
-      <c r="N16" s="20" t="n"/>
-      <c r="O16" s="20" t="n"/>
-      <c r="P16" s="20" t="n"/>
-      <c r="Q16" s="20" t="n"/>
-      <c r="R16" s="20" t="n"/>
+      <c r="H16" s="14" t="inlineStr"/>
+      <c r="I16" s="14" t="inlineStr"/>
+      <c r="J16" s="14" t="inlineStr"/>
+      <c r="K16" s="14" t="inlineStr"/>
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>AI1(b)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Responsible AI</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Improve understanding of our sustainability-related risks and opportunities of AI technologies by 2028.</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Case studies of sustainability and AI-related education, research and collaboration activities.</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>Please provide case studies from your Faculty/Portfolio of sustainability and AI-related education, research or collaboration activities, describing the activity, participants or partners, sustainability issue addressed and key outcomes or lessons.</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>We will select examples of sustainability and AI-related education, research and collaboration as case studies for the new Responsible AI section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H17" s="19" t="inlineStr"/>
-      <c r="I17" s="19" t="inlineStr"/>
-      <c r="J17" s="19" t="inlineStr"/>
-      <c r="K17" s="19" t="inlineStr"/>
-      <c r="L17" s="20" t="n"/>
-      <c r="M17" s="20" t="n"/>
-      <c r="N17" s="20" t="n"/>
-      <c r="O17" s="20" t="n"/>
-      <c r="P17" s="20" t="n"/>
-      <c r="Q17" s="20" t="n"/>
-      <c r="R17" s="20" t="n"/>
+      <c r="H17" s="14" t="inlineStr"/>
+      <c r="I17" s="14" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="14" t="inlineStr"/>
+      <c r="L17" s="15" t="n"/>
+      <c r="M17" s="15" t="n"/>
+      <c r="N17" s="15" t="n"/>
+      <c r="O17" s="15" t="n"/>
+      <c r="P17" s="15" t="n"/>
+      <c r="Q17" s="15" t="n"/>
     </row>
     <row r="18" ht="150" customHeight="1">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr"/>
-      <c r="I18" s="19" t="inlineStr"/>
-      <c r="J18" s="19" t="inlineStr"/>
-      <c r="K18" s="19" t="inlineStr"/>
-      <c r="L18" s="20" t="n"/>
-      <c r="M18" s="20" t="n"/>
-      <c r="N18" s="20" t="n"/>
-      <c r="O18" s="20" t="n"/>
-      <c r="P18" s="20" t="n"/>
-      <c r="Q18" s="20" t="n"/>
-      <c r="R18" s="20" t="n"/>
+      <c r="H18" s="14" t="inlineStr"/>
+      <c r="I18" s="14" t="inlineStr"/>
+      <c r="J18" s="14" t="inlineStr"/>
+      <c r="K18" s="14" t="inlineStr"/>
+      <c r="L18" s="15" t="n"/>
+      <c r="M18" s="15" t="n"/>
+      <c r="N18" s="15" t="n"/>
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
     </row>
     <row r="19" ht="150" customHeight="1">
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>EN1(d)</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Sustainability objectives integrated into governance and decision‑making processes, supported by transparent reporting.</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>Please provide evidence of how sustainability objectives are integrated into governance and decision-making within your Faculty/Portfolio, could include relevant committees, policies, planning or approval processes, accountability mechanisms and examples of transparent reporting.</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>We will report on how sustainability is integrated into governance and decision-making across faculties and portfolios, and use responses as a baseline for the governance enabler from 2027.</t>
         </is>
       </c>
-      <c r="H19" s="19" t="inlineStr"/>
-      <c r="I19" s="19" t="inlineStr"/>
-      <c r="J19" s="19" t="inlineStr"/>
-      <c r="K19" s="19" t="inlineStr"/>
-      <c r="L19" s="20" t="n"/>
-      <c r="M19" s="20" t="n"/>
-      <c r="N19" s="20" t="n"/>
-      <c r="O19" s="20" t="n"/>
-      <c r="P19" s="20" t="n"/>
-      <c r="Q19" s="20" t="n"/>
-      <c r="R19" s="20" t="n"/>
+      <c r="H19" s="14" t="inlineStr"/>
+      <c r="I19" s="14" t="inlineStr"/>
+      <c r="J19" s="14" t="inlineStr"/>
+      <c r="K19" s="14" t="inlineStr"/>
+      <c r="L19" s="15" t="n"/>
+      <c r="M19" s="15" t="n"/>
+      <c r="N19" s="15" t="n"/>
+      <c r="O19" s="15" t="n"/>
+      <c r="P19" s="15" t="n"/>
+      <c r="Q19" s="15" t="n"/>
     </row>
     <row r="20"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="9">
-    <mergeCell ref="M7:N7"/>
+  <mergeCells count="4">
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="L13:R13"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D4:G8"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="L16:L19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$B$3:$B$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q16:Q19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+  <dataValidations count="1">
+    <dataValidation sqref="P16:P19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -1117,7 +1013,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting</t>
+          <t>SR26 sustainability reporting</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1025,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
@@ -1142,77 +1038,77 @@
     </row>
     <row r="6"/>
     <row r="8">
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="23" t="inlineStr"/>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr"/>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="20" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="20" t="n"/>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1263,21 +1159,21 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>No end-2025 request was issued to this area (new to Sustainability 2030 reporting).</t>
         </is>
@@ -1300,13 +1196,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I9"/>
+  <dimension ref="B1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>End 2026 target status</t>
+          <t>(not used – no target status rating in 2026)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -1322,21 +1218,6 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Y/N</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response count</t>
         </is>
       </c>
     </row>
@@ -1361,24 +1242,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1394,24 +1259,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -1427,47 +1276,15 @@
           <t>TBC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
@@ -1475,11 +1292,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>

--- a/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.14)</t>
+          <t>SR26 sustainability reporting (v0.15)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.15)</t>
+          <t>SR26 sustainability reporting (v0.16)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
@@ -20,21 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="00002060"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -170,58 +162,56 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -609,32 +599,22 @@
     <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting (v0.16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -650,321 +630,324 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="60" customHeight="1"/>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11" ht="39" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>CIOG – Responsible AI &amp; digital</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="C13" s="7" t="inlineStr">
+    <row r="12"/>
+    <row r="13" ht="27" customHeight="1">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="10" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="10" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="11" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr"/>
-      <c r="D15" s="11" t="inlineStr"/>
-      <c r="E15" s="11" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="11" t="inlineStr"/>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr"/>
-      <c r="K15" s="11" t="inlineStr"/>
-      <c r="L15" s="11" t="inlineStr">
+    <row r="15" ht="81" customHeight="1">
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="P15" s="9" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="9" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>AI1(a)</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Responsible AI</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Improve understanding of our sustainability-related risks and opportunities of AI technologies by 2028.</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Established measurement of estimated operational impacts and opportunities (eg operational impacts could include energy, water, emissions and intensity measures)</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>(Reporting request TBC)</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>We will provide a high-level overview of AI's estimated operational impacts and opportunities in 2026, ahead of more detailed measurement from 2027.</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr"/>
-      <c r="I16" s="14" t="inlineStr"/>
-      <c r="J16" s="14" t="inlineStr"/>
-      <c r="K16" s="14" t="inlineStr"/>
-      <c r="L16" s="15" t="n"/>
-      <c r="M16" s="15" t="n"/>
-      <c r="N16" s="15" t="n"/>
-      <c r="O16" s="15" t="n"/>
-      <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="15" t="n"/>
+      <c r="H16" s="12" t="inlineStr"/>
+      <c r="I16" s="12" t="inlineStr"/>
+      <c r="J16" s="12" t="inlineStr"/>
+      <c r="K16" s="12" t="inlineStr"/>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="13" t="n"/>
+      <c r="O16" s="13" t="n"/>
+      <c r="P16" s="13" t="n"/>
+      <c r="Q16" s="13" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>AI1(b)</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Responsible AI</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Improve understanding of our sustainability-related risks and opportunities of AI technologies by 2028.</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Case studies of sustainability and AI-related education, research and collaboration activities.</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Please provide case studies from your Faculty/Portfolio of sustainability and AI-related education, research or collaboration activities, describing the activity, participants or partners, sustainability issue addressed and key outcomes or lessons.</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>We will select examples of sustainability and AI-related education, research and collaboration as case studies for the new Responsible AI section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr"/>
-      <c r="I17" s="14" t="inlineStr"/>
-      <c r="J17" s="14" t="inlineStr"/>
-      <c r="K17" s="14" t="inlineStr"/>
-      <c r="L17" s="15" t="n"/>
-      <c r="M17" s="15" t="n"/>
-      <c r="N17" s="15" t="n"/>
-      <c r="O17" s="15" t="n"/>
-      <c r="P17" s="15" t="n"/>
-      <c r="Q17" s="15" t="n"/>
+      <c r="H17" s="12" t="inlineStr"/>
+      <c r="I17" s="12" t="inlineStr"/>
+      <c r="J17" s="12" t="inlineStr"/>
+      <c r="K17" s="12" t="inlineStr"/>
+      <c r="L17" s="13" t="n"/>
+      <c r="M17" s="13" t="n"/>
+      <c r="N17" s="13" t="n"/>
+      <c r="O17" s="13" t="n"/>
+      <c r="P17" s="13" t="n"/>
+      <c r="Q17" s="13" t="n"/>
     </row>
     <row r="18" ht="150" customHeight="1">
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr"/>
-      <c r="I18" s="14" t="inlineStr"/>
-      <c r="J18" s="14" t="inlineStr"/>
-      <c r="K18" s="14" t="inlineStr"/>
-      <c r="L18" s="15" t="n"/>
-      <c r="M18" s="15" t="n"/>
-      <c r="N18" s="15" t="n"/>
-      <c r="O18" s="15" t="n"/>
-      <c r="P18" s="15" t="n"/>
-      <c r="Q18" s="15" t="n"/>
+      <c r="H18" s="12" t="inlineStr"/>
+      <c r="I18" s="12" t="inlineStr"/>
+      <c r="J18" s="12" t="inlineStr"/>
+      <c r="K18" s="12" t="inlineStr"/>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="13" t="n"/>
+      <c r="N18" s="13" t="n"/>
+      <c r="O18" s="13" t="n"/>
+      <c r="P18" s="13" t="n"/>
+      <c r="Q18" s="13" t="n"/>
     </row>
     <row r="19" ht="150" customHeight="1">
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>EN1(d)</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Sustainability objectives integrated into governance and decision‑making processes, supported by transparent reporting.</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Please provide evidence of how sustainability objectives are integrated into governance and decision-making within your Faculty/Portfolio, could include relevant committees, policies, planning or approval processes, accountability mechanisms and examples of transparent reporting.</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>We will report on how sustainability is integrated into governance and decision-making across faculties and portfolios, and use responses as a baseline for the governance enabler from 2027.</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr"/>
-      <c r="I19" s="14" t="inlineStr"/>
-      <c r="J19" s="14" t="inlineStr"/>
-      <c r="K19" s="14" t="inlineStr"/>
-      <c r="L19" s="15" t="n"/>
-      <c r="M19" s="15" t="n"/>
-      <c r="N19" s="15" t="n"/>
-      <c r="O19" s="15" t="n"/>
-      <c r="P19" s="15" t="n"/>
-      <c r="Q19" s="15" t="n"/>
+      <c r="H19" s="12" t="inlineStr"/>
+      <c r="I19" s="12" t="inlineStr"/>
+      <c r="J19" s="12" t="inlineStr"/>
+      <c r="K19" s="12" t="inlineStr"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="13" t="n"/>
+      <c r="N19" s="13" t="n"/>
+      <c r="O19" s="13" t="n"/>
+      <c r="P19" s="13" t="n"/>
+      <c r="Q19" s="13" t="n"/>
     </row>
     <row r="20"/>
   </sheetData>
@@ -1005,110 +988,102 @@
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="16" t="inlineStr">
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="8">
-      <c r="B8" s="18" t="inlineStr">
+    <row r="7"/>
+    <row r="8" ht="39" customHeight="1">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="19" t="inlineStr"/>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr"/>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr"/>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr"/>
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr"/>
+      <c r="F9" s="17" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1139,41 +1114,30 @@
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>End-2025 target status assessment and reporting (for reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Your SR25 responses – Chief Information Officer Group (CIOG)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="20" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="21" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>No end-2025 request was issued to this area (new to Sustainability 2030 reporting).</t>
         </is>
@@ -1196,10 +1160,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="B1" t="inlineStr">
         <is>
           <t>(not used – no target status rating in 2026)</t>
@@ -1221,7 +1192,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="22" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
           <t>Please select from dropdown</t>
@@ -1243,7 +1214,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1260,7 +1231,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="22" customHeight="1">
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -1277,35 +1248,35 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="D8" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="D9" t="inlineStr">
         <is>
           <t>Not required</t>

--- a/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
@@ -622,7 +622,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
@@ -31,7 +31,7 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00002060"/>
+      <color rgb="00FFFFFF"/>
       <sz val="22"/>
     </font>
     <font>
@@ -102,7 +102,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -127,6 +127,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C1E4F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00000F46"/>
       </patternFill>
     </fill>
   </fills>
@@ -162,9 +167,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="4"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -286,6 +294,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -577,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -597,24 +695,61 @@
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -622,7 +757,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Thursday 24 December 2026 (Christmas shutdown). Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>
@@ -633,7 +768,7 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11" ht="39" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>CIOG – Responsible AI &amp; digital</t>
         </is>
@@ -641,313 +776,313 @@
     </row>
     <row r="12"/>
     <row r="13" ht="27" customHeight="1">
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="P14" s="9" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="Q14" s="9" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="81" customHeight="1">
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="9" t="inlineStr"/>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr"/>
-      <c r="J15" s="9" t="inlineStr"/>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="9" t="inlineStr">
+      <c r="O15" s="10" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="9" t="inlineStr">
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="9" t="inlineStr">
+      <c r="Q15" s="10" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>AI1(a)</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Responsible AI</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Improve understanding of our sustainability-related risks and opportunities of AI technologies by 2028.</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Established measurement of estimated operational impacts and opportunities (eg operational impacts could include energy, water, emissions and intensity measures)</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>(Reporting request TBC)</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>We will provide a high-level overview of AI's estimated operational impacts and opportunities in 2026, ahead of more detailed measurement from 2027.</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr"/>
-      <c r="I16" s="12" t="inlineStr"/>
-      <c r="J16" s="12" t="inlineStr"/>
-      <c r="K16" s="12" t="inlineStr"/>
-      <c r="L16" s="13" t="n"/>
-      <c r="M16" s="13" t="n"/>
-      <c r="N16" s="13" t="n"/>
-      <c r="O16" s="13" t="n"/>
-      <c r="P16" s="13" t="n"/>
-      <c r="Q16" s="13" t="n"/>
+      <c r="H16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr"/>
+      <c r="J16" s="13" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
+      <c r="P16" s="14" t="n"/>
+      <c r="Q16" s="14" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>AI1(b)</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Responsible AI</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Improve understanding of our sustainability-related risks and opportunities of AI technologies by 2028.</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Case studies of sustainability and AI-related education, research and collaboration activities.</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Please provide case studies from your Faculty/Portfolio of sustainability and AI-related education, research or collaboration activities, describing the activity, participants or partners, sustainability issue addressed and key outcomes or lessons.</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>We will select examples of sustainability and AI-related education, research and collaboration as case studies for the new Responsible AI section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="12" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr"/>
-      <c r="K17" s="12" t="inlineStr"/>
-      <c r="L17" s="13" t="n"/>
-      <c r="M17" s="13" t="n"/>
-      <c r="N17" s="13" t="n"/>
-      <c r="O17" s="13" t="n"/>
-      <c r="P17" s="13" t="n"/>
-      <c r="Q17" s="13" t="n"/>
+      <c r="H17" s="13" t="inlineStr"/>
+      <c r="I17" s="13" t="inlineStr"/>
+      <c r="J17" s="13" t="inlineStr"/>
+      <c r="K17" s="13" t="inlineStr"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="14" t="n"/>
+      <c r="P17" s="14" t="n"/>
+      <c r="Q17" s="14" t="n"/>
     </row>
     <row r="18" ht="150" customHeight="1">
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr"/>
-      <c r="I18" s="12" t="inlineStr"/>
-      <c r="J18" s="12" t="inlineStr"/>
-      <c r="K18" s="12" t="inlineStr"/>
-      <c r="L18" s="13" t="n"/>
-      <c r="M18" s="13" t="n"/>
-      <c r="N18" s="13" t="n"/>
-      <c r="O18" s="13" t="n"/>
-      <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="13" t="n"/>
+      <c r="H18" s="13" t="inlineStr"/>
+      <c r="I18" s="13" t="inlineStr"/>
+      <c r="J18" s="13" t="inlineStr"/>
+      <c r="K18" s="13" t="inlineStr"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
+      <c r="N18" s="14" t="n"/>
+      <c r="O18" s="14" t="n"/>
+      <c r="P18" s="14" t="n"/>
+      <c r="Q18" s="14" t="n"/>
     </row>
     <row r="19" ht="150" customHeight="1">
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>EN1(d)</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Sustainability objectives integrated into governance and decision‑making processes, supported by transparent reporting.</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Please provide evidence of how sustainability objectives are integrated into governance and decision-making within your Faculty/Portfolio, could include relevant committees, policies, planning or approval processes, accountability mechanisms and examples of transparent reporting.</t>
         </is>
       </c>
-      <c r="G19" s="12" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>We will report on how sustainability is integrated into governance and decision-making across faculties and portfolios, and use responses as a baseline for the governance enabler from 2027.</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr"/>
-      <c r="I19" s="12" t="inlineStr"/>
-      <c r="J19" s="12" t="inlineStr"/>
-      <c r="K19" s="12" t="inlineStr"/>
-      <c r="L19" s="13" t="n"/>
-      <c r="M19" s="13" t="n"/>
-      <c r="N19" s="13" t="n"/>
-      <c r="O19" s="13" t="n"/>
-      <c r="P19" s="13" t="n"/>
-      <c r="Q19" s="13" t="n"/>
+      <c r="H19" s="13" t="inlineStr"/>
+      <c r="I19" s="13" t="inlineStr"/>
+      <c r="J19" s="13" t="inlineStr"/>
+      <c r="K19" s="13" t="inlineStr"/>
+      <c r="L19" s="14" t="n"/>
+      <c r="M19" s="14" t="n"/>
+      <c r="N19" s="14" t="n"/>
+      <c r="O19" s="14" t="n"/>
+      <c r="P19" s="14" t="n"/>
+      <c r="Q19" s="14" t="n"/>
     </row>
     <row r="20"/>
   </sheetData>
@@ -964,6 +1099,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -973,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -986,104 +1122,148 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4"/>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Thursday 24 December 2026 (Christmas shutdown) (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="39" customHeight="1">
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="17" t="inlineStr"/>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1091,6 +1271,7 @@
     <mergeCell ref="C5:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1100,7 +1281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1112,32 +1293,77 @@
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Your SR25 responses – Chief Information Officer Group (CIOG)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>No end-2025 request was issued to this area (new to Sustainability 2030 reporting).</t>
         </is>
@@ -1151,6 +1377,7 @@
     <hyperlink ref="B4" location="'1. Reporting template'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIOG - SR26 sustainability reporting request.xlsx
@@ -692,9 +692,9 @@
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -753,7 +753,8 @@
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
-• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
+• Note the source of your information, any limitations and the person closest to the data (Column O)
+• Please return the spreadsheet once it has been reviewed and confirmed by your area's senior lead
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
@@ -792,7 +793,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
@@ -860,17 +861,7 @@
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>Data source and limitations</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>Data owner confirms information is accurate</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>Confirmed by (name, role, date)</t>
+          <t>Data source, limitations and contact person</t>
         </is>
       </c>
     </row>
@@ -902,17 +893,7 @@
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
-        <is>
-          <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
-        </is>
-      </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>Name, role and date of the person confirming</t>
+          <t>Where did this information come from (system, report, survey)? Note any gaps or limitations, and the person closest to the data we can follow up with.</t>
         </is>
       </c>
     </row>
@@ -955,8 +936,6 @@
       <c r="M16" s="14" t="n"/>
       <c r="N16" s="14" t="n"/>
       <c r="O16" s="14" t="n"/>
-      <c r="P16" s="14" t="n"/>
-      <c r="Q16" s="14" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
@@ -981,7 +960,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>Please provide case studies from your Faculty/Portfolio of sustainability and AI-related education, research or collaboration activities, describing the activity, participants or partners, sustainability issue addressed and key outcomes or lessons.</t>
+          <t>Please provide case studies from your portfolio of sustainability and AI-related education, research or collaboration activities, describing the activity, participants or partners, sustainability issue addressed and key outcomes or lessons.</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
@@ -997,8 +976,6 @@
       <c r="M17" s="14" t="n"/>
       <c r="N17" s="14" t="n"/>
       <c r="O17" s="14" t="n"/>
-      <c r="P17" s="14" t="n"/>
-      <c r="Q17" s="14" t="n"/>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="B18" s="11" t="inlineStr">
@@ -1023,12 +1000,12 @@
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
+          <t>Please provide examples of internal engagement or external partnerships involving your portfolio that contributed to sustainability outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
+          <t>We will report on internal engagement and partnerships contributing to sustainability outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr"/>
@@ -1039,8 +1016,6 @@
       <c r="M18" s="14" t="n"/>
       <c r="N18" s="14" t="n"/>
       <c r="O18" s="14" t="n"/>
-      <c r="P18" s="14" t="n"/>
-      <c r="Q18" s="14" t="n"/>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="B19" s="11" t="inlineStr">
@@ -1065,7 +1040,7 @@
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>Please provide evidence of how sustainability objectives are integrated into governance and decision-making within your Faculty/Portfolio, could include relevant committees, policies, planning or approval processes, accountability mechanisms and examples of transparent reporting.</t>
+          <t>Please provide evidence of how sustainability objectives are integrated into governance and decision-making within your portfolio, could include relevant committees, policies, planning or approval processes, accountability mechanisms and examples of transparent reporting.</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
@@ -1081,23 +1056,16 @@
       <c r="M19" s="14" t="n"/>
       <c r="N19" s="14" t="n"/>
       <c r="O19" s="14" t="n"/>
-      <c r="P19" s="14" t="n"/>
-      <c r="Q19" s="14" t="n"/>
     </row>
     <row r="20"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="4">
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="L13:O13"/>
     <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="P16:P19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$C$2:$C$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
